--- a/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Programkurser olankade" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olankade'!$A$1:$E$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E172"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Valbara eller valfria litteraturvetenskapligt inriktade kurser` (30 hp); rad: - Valbara eller valfria litteraturvetenskapligt inriktade kurser, 30 hp</t>
+          <t>Programtext `Franskspråkig chanson i original och översättning` ≠ kursplanens namn `Franska IV: Franskspråkig chanson i original och översättning` (kurskod `AFR27P`); rad: - [[AFR27P|Franskspråkig chanson i original och översättning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`Valbara och valfria litteraturvetenskapligt inriktade kurser` (30 hp); rad: - Valbara och valfria litteraturvetenskapligt inriktade kurser, 30 hp</t>
+          <t>Programtext `Franskspråkig litteraturkritik` ≠ kursplanens namn `Franska IV: Franskspråkig litteraturkritik` (kurskod `AFR26Q`); rad: - [[AFR26Q|Franskspråkig litteraturkritik]], 7,5 hp</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>HSVAA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Valbar eller valfri kurs inom franskspråkig litteratur` (7,5 hp); rad: - Valbar eller valfri kurs inom franskspråkig litteratur, 7,5 hp</t>
+          <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp); rad: - Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HSVAA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>HTESA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`Valbar eller valfri kurs inom tyskspråkig litteratur` (7,5 hp); rad: - Valbar eller valfri kurs inom tyskspråkig litteratur, 7,5 hp</t>
+          <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp); rad: - Kärnområden i tillämpad engelsk lingvistik, 7,5 hp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>HTESA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Programtext `Franskspråkig chanson i original och översättning` ≠ kursplanens namn `Franska IV: Franskspråkig chanson i original och översättning` (kurskod `AFR27P`); rad: - [[AFR27P|Franskspråkig chanson i original och översättning]], 7,5 hp</t>
+          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>HTESA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Programtext `Franskspråkig litteraturkritik` ≠ kursplanens namn `Franska IV: Franskspråkig litteraturkritik` (kurskod `AFR26Q`); rad: - [[AFR26Q|Franskspråkig litteraturkritik]], 7,5 hp</t>
+          <t>Programtext `Diskursanalys` ≠ kursplanens namn `Engelska: Diskursanalys` (kurskod `EN3072`); rad: - [[EN3072|Diskursanalys]], 7,5 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HSVAA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp); rad: - Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv, 7,5 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HSVAA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HTESA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp); rad: - Kärnområden i tillämpad engelsk lingvistik, 7,5 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>HTESA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>HTESA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Programtext `Diskursanalys` ≠ kursplanens namn `Engelska: Diskursanalys` (kurskod `EN3072`); rad: - [[EN3072|Diskursanalys]], 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - &lt;a class="no-graph" href="GPG32A"&gt;Skolväsendets historia och samhällsuppdrag – ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - &lt;a class="no-graph" href="GPG32A"&gt;Skolväsendets historia och samhällsuppdrag – ämneslärare&lt;/a&gt;, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - &lt;a class="no-graph" href="GPG32A"&gt;Skolväsendets historia och samhällsuppdrag – ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2480,17 +2480,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - &lt;a class="no-graph" href="GPG32A"&gt;Skolväsendets historia och samhällsuppdrag – ämneslärare&lt;/a&gt;, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp); rad: - Engelska för grundlärare åk 4-6 1A, 15 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp); rad: - Engelska för grundlärare åk 4-6 1B, 15 hp</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i grundskolan åk 4–6` ≠ kursplanens namn `Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`); rad: - &lt;a class="no-graph" href="GPG2LZ"&gt;Sociala relationer, konflikter och makt i grundskolan åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp); rad: - Engelska för grundlärare åk 4-6 1A, 15 hp</t>
+          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp); rad: - Engelska för grundlärare åk 4-6 1B, 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
+          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i grundskolan åk 4–6` ≠ kursplanens namn `Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`); rad: - &lt;a class="no-graph" href="GPG2LZ"&gt;Sociala relationer, konflikter och makt i grundskolan åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2912,24 +2912,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,24 +2939,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3182,24 +3182,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3209,24 +3209,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3236,24 +3236,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3295,19 +3295,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3452,24 +3452,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3479,24 +3479,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3560,24 +3560,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3587,17 +3587,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -3803,12 +3803,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
+          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4019,24 +4019,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4046,24 +4046,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4073,24 +4073,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4100,24 +4100,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4127,24 +4127,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4154,17 +4154,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
+          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4591,19 +4591,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4618,19 +4618,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
+          <t>Programtext `Kunskap, lärande och bedömning – KPU` ≠ kursplanens namn `Kunskap, lärande och bedömning - KPU` (kurskod `GPG2S7`); rad: - &lt;a class="no-graph" href="GPG2S7"&gt;Kunskap, lärande och bedömning – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4645,19 +4645,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4672,19 +4672,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4699,19 +4699,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,19 +4726,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>LU79A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4753,19 +4753,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Kunskap, lärande och bedömning – KPU` ≠ kursplanens namn `Kunskap, lärande och bedömning - KPU` (kurskod `GPG2S7`); rad: - &lt;a class="no-graph" href="GPG2S7"&gt;Kunskap, lärande och bedömning – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>LU79A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4780,19 +4780,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Programtext `Kunskap, lärande och bedömning – KPU` ≠ kursplanens namn `Kunskap, lärande och bedömning - KPU` (kurskod `GPG2S7`); rad: - &lt;a class="no-graph" href="GPG2S7"&gt;Kunskap, lärande och bedömning – KPU&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>LU79A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4807,19 +4807,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>LU79A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>LU79A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4856,24 +4856,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
+          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>LUGYA</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4883,24 +4883,24 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
+          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>LUGYA</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4910,184 +4910,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Programtext `Kunskap, lärande och bedömning – KPU` ≠ kursplanens namn `Kunskap, lärande och bedömning - KPU` (kurskod `GPG2S7`); rad: - &lt;a class="no-graph" href="GPG2S7"&gt;Kunskap, lärande och bedömning – KPU&lt;/a&gt;, 15 hp</t>
+          <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E172"/>
+  <autoFilter ref="A1:E166"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -5419,18 +5257,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E166"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1984,7 +1984,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,17 +1994,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - &lt;a class="no-graph" href="GPG32A"&gt;Skolväsendets historia och samhällsuppdrag – ämneslärare&lt;/a&gt;, 15 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2318,17 +2318,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - &lt;a class="no-graph" href="GPG32A"&gt;Skolväsendets historia och samhällsuppdrag – ämneslärare&lt;/a&gt;, 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp); rad: - Engelska för grundlärare åk 4-6 1A, 15 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp); rad: - Engelska för grundlärare åk 4-6 1B, 15 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp); rad: - Engelska för grundlärare åk 4-6 1A, 15 hp</t>
+          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp); rad: - Engelska för grundlärare åk 4-6 1B, 15 hp</t>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i grundskolan åk 4–6` ≠ kursplanens namn `Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`); rad: - &lt;a class="no-graph" href="GPG2LZ"&gt;Sociala relationer, konflikter och makt i grundskolan åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i grundskolan åk 4–6` ≠ kursplanens namn `Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`); rad: - &lt;a class="no-graph" href="GPG2LZ"&gt;Sociala relationer, konflikter och makt i grundskolan åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2669,24 +2669,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,24 +2696,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2755,19 +2755,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3128,24 +3128,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3155,24 +3155,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,19 +3214,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3263,24 +3263,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3290,24 +3290,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3317,24 +3317,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3344,24 +3344,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3376,19 +3376,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3403,19 +3403,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -3469,7 +3469,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3484,19 +3484,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3511,19 +3511,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3538,19 +3538,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3565,19 +3565,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3619,19 +3619,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3668,24 +3668,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
+          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3695,24 +3695,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3732,14 +3732,14 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,19 +3835,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3862,19 +3862,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3889,19 +3889,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3916,19 +3916,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3943,19 +3943,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3970,19 +3970,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4019,24 +4019,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4051,19 +4051,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,19 +4078,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4105,827 +4105,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - &lt;a class="no-graph" href="GPG3CK"&gt;Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Programtext `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6` ≠ kursplanens namn `Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4-6` (kurskod `PG3025`); rad: - &lt;a class="no-graph" href="PG3025"&gt;Specialpedagogik, pedagogisk dokumentation och bedömning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4-6` (kurskod `APG245`); rad: - &lt;a class="no-graph" href="APG245"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Programtext `Matematik 1a för grundlärare 4–6` ≠ kursplanens namn `Matematik 1a för grundlärare 4-6` (kurskod `GMD2HH`); rad: - &lt;a class="no-graph" href="GMD2HH"&gt;Matematik 1a för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Programtext `Matematik 1b för grundlärare 4–6` ≠ kursplanens namn `Matematik 1b för grundlärare 4-6` (kurskod `GMD2HJ`); rad: - &lt;a class="no-graph" href="GMD2HJ"&gt;Matematik 1b för grundlärare 4–6&lt;/a&gt;, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Programtext `Matematik 2 för grundlärare 4–6` ≠ kursplanens namn `Matematik 2 för grundlärare 4-6` (kurskod `GMD2HK`); rad: - &lt;a class="no-graph" href="GMD2HK"&gt;Matematik 2 för grundlärare 4–6&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Programtext `Bild för grundlärare, årskurs 4–6` ≠ kursplanens namn `Bild för grundlärare, årskurs 4-6` (kurskod `GBP32U`); rad: - &lt;a class="no-graph" href="GBP32U"&gt;Bild för grundlärare, årskurs 4–6&lt;/a&gt;, 30 hp</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Programtext `Naturorienterande ämnen och teknik för grundlärare, åk 4–6` ≠ kursplanens namn `Naturorienterande ämnen och teknik för grundlärare, åk 4-6` (kurskod `GNV367`); rad: - &lt;a class="no-graph" href="GNV367"&gt;Naturorienterande ämnen och teknik för grundlärare, åk 4–6&lt;/a&gt;, 30 hp</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Programtext `Kunskap, lärande och bedömning – KPU` ≠ kursplanens namn `Kunskap, lärande och bedömning - KPU` (kurskod `GPG2S7`); rad: - &lt;a class="no-graph" href="GPG2S7"&gt;Kunskap, lärande och bedömning – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Programtext `Kunskap, lärande och bedömning – KPU` ≠ kursplanens namn `Kunskap, lärande och bedömning - KPU` (kurskod `GPG2S7`); rad: - &lt;a class="no-graph" href="GPG2S7"&gt;Kunskap, lärande och bedömning – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E166"/>
+  <autoFilter ref="A1:E136"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -5197,66 +4387,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>HMILA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Magisterprojektets planering` (1 hp); rad: - Magisterprojektets planering, 1 hp</t>
+          <t>Programtext `Franskspråkig chanson i original och översättning` ≠ kursplanens namn `Franska IV: Franskspråkig chanson i original och översättning` (kurskod `AFR27P`); rad: - [[AFR27P|Franskspråkig chanson i original och översättning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>HMILA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,24 +509,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Den vidareutvecklade uppsatsplanen` (1 hp); rad: - Den vidareutvecklade uppsatsplanen, 1 hp</t>
+          <t>Programtext `Franskspråkig litteraturkritik` ≠ kursplanens namn `Franska IV: Franskspråkig litteraturkritik` (kurskod `AFR26Q`); rad: - [[AFR26Q|Franskspråkig litteraturkritik]], 7,5 hp</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>HSVAA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Magisterexamensarbete i Afrikanska studier` (15 hp); rad: - Magisterexamensarbete i Afrikanska studier, 15 hp</t>
+          <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp); rad: - Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HSVAA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>HTESA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Bistånd och utveckling i Afrika söder om Sahara` (7 hp); rad: - Bistånd och utveckling i Afrika söder om Sahara, 7 hp</t>
+          <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp); rad: - Kärnområden i tillämpad engelsk lingvistik, 7,5 hp</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>HTESA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -590,24 +590,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Egypten och medierna` (7 hp); rad: - Egypten och medierna, 7 hp</t>
+          <t>Programtext `Diskursanalys` ≠ kursplanens namn `Engelska: Diskursanalys` (kurskod `EN3072`); rad: - [[EN3072|Diskursanalys]], 7,5 hp</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik` (7 hp); rad: - Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik, 7 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Den nordafrikanska novellen` (7 hp); rad: - Den nordafrikanska novellen, 7 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Islam och muslimska samhällen i Afrika` (7 hp); rad: - Islam och muslimska samhällen i Afrika, 7 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Språk och nationalitet i afrikanska flerspråkliga länder` (7 hp); rad: - Språk och nationalitet i afrikanska flerspråkliga länder, 7 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Södra Afrikas moderna historia` (7 hp); rad: - Södra Afrikas moderna historia, 7 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Afrikas horn` (7 hp); rad: - Afrikas horn, 7 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Fred och konflikt i Afrika: Internationell institutionell lag` (7 hp); rad: - Fred och konflikt i Afrika: Internationell institutionell lag, 7 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Västafrika sedan 1800-talet` (7 hp); rad: - Västafrika sedan 1800-talet, 7 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`_1. Afrikanska samhällen i förändring` (12 hp); rad: - _1. Afrikanska samhällen i förändring, 12 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`_2. Religion och politik i afrikanska samhällen` (9 hp); rad: - _2. Religion och politik i afrikanska samhällen, 9 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`_3. Utbildning och förändring i afrikanska samhällen` (8 hp); rad: - _3. Utbildning och förändring i afrikanska samhällen, 8 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`_4. Magisterprojektets planering` (1 hp); rad: - _4. Magisterprojektets planering, 1 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`_5. Den vidareutvecklade uppsatsplanen` (1 hp); rad: - _5. Den vidareutvecklade uppsatsplanen, 1 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`_6. Magisterexamensarbete i Afrikanska studier` (15 hp); rad: - _6. Magisterexamensarbete i Afrikanska studier, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`_1. Bistånd och utveckling i Afrika söder om Sahara` (7 hp); rad: - _1. Bistånd och utveckling i Afrika söder om Sahara, 7 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp); rad: - Engelska för grundlärare åk 4-6 1A, 15 hp</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`_2. Litteratur och politik i det samtida Afrika` (7 hp); rad: - _2. Litteratur och politik i det samtida Afrika, 7 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp); rad: - Engelska för grundlärare åk 4-6 1B, 15 hp</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`_3. Ekonomisk utveckling i Afrika, en introduktion` (7 hp); rad: - _3. Ekonomisk utveckling i Afrika, en introduktion, 7 hp</t>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`_4. Egypten och medierna` (7 hp); rad: - _4. Egypten och medierna, 7 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i grundskolan åk 4–6` ≠ kursplanens namn `Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`); rad: - &lt;a class="no-graph" href="GPG2LZ"&gt;Sociala relationer, konflikter och makt i grundskolan åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`_5. Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik` (7 hp); rad: - _5. Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik, 7 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`_6. Mänskliga rättigheter och demokrati i Afrika söder om Sahara` (7 hp); rad: - _6. Mänskliga rättigheter och demokrati i Afrika söder om Sahara, 7 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`_7. Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv` (7hp); rad: - _7. Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv, 7hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`_8. Den nordafrikanska novellen` (7 hp); rad: - _8. Den nordafrikanska novellen, 7 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`_9. Islam och muslimska samhällen i Afrika` (7 hp); rad: - _9. Islam och muslimska samhällen i Afrika, 7 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`_10. Språk och nationalitet i afrikanska flerspråkliga länder` (7 hp); rad: - _10. Språk och nationalitet i afrikanska flerspråkliga länder, 7 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`_11. Södra Afrikas moderna historia` (7 hp); rad: - _11. Södra Afrikas moderna historia, 7 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`_12. Afrikas horn` (7 hp); rad: - _12. Afrikas horn, 7 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`_13. Fred och konflikt i Afrika: Internationell institutionell lag` (7 hp); rad: - _13. Fred och konflikt i Afrika: Internationell institutionell lag, 7 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`_14. Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara` (7 hp); rad: - _14. Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara, 7 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`_15. Västafrika sedan 1800-talet` (7 hp); rad: - _15. Västafrika sedan 1800-talet, 7 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Programtext `Afrikanska samhällen i förändring` ≠ kursplanens namn `Afrikanska studier: Afrikanska samhällen i förändring` (kurskod `AS3022`); rad: - [[AS3022|Afrikanska samhällen i förändring]], 12 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Programtext `Religion och politik i afrikanska samhällen` ≠ kursplanens namn `Afrikanska studier: Religion och politik i afrikanska samhällen` (kurskod `AS3023`); rad: - [[AS3023|Religion och politik i afrikanska samhällen]], 9 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Programtext `Utbildning och förändring i afrikanska samhällen` ≠ kursplanens namn `Afrikanska studier: Utbildning och förändring i afrikanska samhällen` (kurskod `AS3021`); rad: - [[AS3021|Utbildning och förändring i afrikanska samhällen]], 8 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Programtext `Litteratur och politik i det samtida Afrika` ≠ kursplanens namn `Afrikanska studier: Litteratur och politik i det samtida Afrika` (kurskod `AS3017`); rad: - [[AS3017|Litteratur och politik i det samtida Afrika]], 7 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Programtext `Ekonomisk utveckling i Afrika, en introduktion` ≠ kursplanens namn `Afrikanska studier: Ekonomisk utveckling i Afrika, en introduktion` (kurskod `AS3019`); rad: - [[AS3019|Ekonomisk utveckling i Afrika, en introduktion]], 7 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Programtext `Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv` ≠ kursplanens namn `Afrikanska studier: Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv` (kurskod `AS3014`); rad: - [[AS3014|Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv]], 7hp</t>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Programtext `Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara` ≠ kursplanens namn `Afrikanska studier: Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara` (kurskod `AS3018`); rad: - [[AS3018|Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara]], 7 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Programtext `Franskspråkig chanson i original och översättning` ≠ kursplanens namn `Franska IV: Franskspråkig chanson i original och översättning` (kurskod `AFR27P`); rad: - [[AFR27P|Franskspråkig chanson i original och översättning]], 7,5 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Programtext `Franskspråkig litteraturkritik` ≠ kursplanens namn `Franska IV: Franskspråkig litteraturkritik` (kurskod `AFR26Q`); rad: - [[AFR26Q|Franskspråkig litteraturkritik]], 7,5 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HSVAA</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp); rad: - Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv, 7,5 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HSVAA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HTESA</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp); rad: - Kärnområden i tillämpad engelsk lingvistik, 7,5 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HTESA</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HTESA</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Programtext `Diskursanalys` ≠ kursplanens namn `Engelska: Diskursanalys` (kurskod `EN3072`); rad: - [[EN3072|Diskursanalys]], 7,5 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,24 +2156,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2210,24 +2210,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2291,24 +2291,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2345,24 +2345,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2372,24 +2372,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2399,24 +2399,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp); rad: - Engelska för grundlärare åk 4-6 1A, 15 hp</t>
+          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp); rad: - Engelska för grundlärare åk 4-6 1B, 15 hp</t>
+          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,1637 +2485,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
+          <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>LL46A</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>LL46A</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i grundskolan åk 4–6` ≠ kursplanens namn `Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`); rad: - &lt;a class="no-graph" href="GPG2LZ"&gt;Sociala relationer, konflikter och makt i grundskolan åk 4–6&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>LL46A</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>LL46A</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>LL46A</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>LLF3A</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>LLF3A</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>LLF3A</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>LLF3A</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>LLF3A</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>LLF3A</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>LLF3A</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>LLF3A</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>LLF3A</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>LLL3A</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>LLL3A</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>LLL3A</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>LLL3A</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>LLL3A</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>LLL3A</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>LLL3A</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>LLL3A</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>LLL3A</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>LLL6A</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>`Idrott för grundlärare, årskurs 4–6` (30 hp); rad: - Idrott för grundlärare, årskurs 4–6, 30 hp</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E136"/>
+  <autoFilter ref="A1:E76"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4267,126 +2647,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>HSVAA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Programtext `Franskspråkig chanson i original och översättning` ≠ kursplanens namn `Franska IV: Franskspråkig chanson i original och översättning` (kurskod `AFR27P`); rad: - [[AFR27P|Franskspråkig chanson i original och översättning]], 7,5 hp</t>
+          <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp); rad: - Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HSVAA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HMILA</t>
+          <t>HTESA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,24 +509,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Programtext `Franskspråkig litteraturkritik` ≠ kursplanens namn `Franska IV: Franskspråkig litteraturkritik` (kurskod `AFR26Q`); rad: - [[AFR26Q|Franskspråkig litteraturkritik]], 7,5 hp</t>
+          <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp); rad: - Kärnområden i tillämpad engelsk lingvistik, 7,5 hp</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HMILA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HSVAA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp); rad: - Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv, 7,5 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HSVAA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HTESA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp); rad: - Kärnområden i tillämpad engelsk lingvistik, 7,5 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HTESA</t>
+          <t>LG79A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -590,17 +590,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Programtext `Diskursanalys` ≠ kursplanens namn `Engelska: Diskursanalys` (kurskod `EN3072`); rad: - [[EN3072|Diskursanalys]], 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>LG79A</t>
+          <t>LGGYA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LGGYA</t>
+          <t>LL46A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp); rad: - Engelska för grundlärare åk 4-6 1A, 15 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp); rad: - Engelska för grundlärare åk 4-6 1B, 15 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp); rad: - Engelska för grundlärare åk 4-6 1A, 15 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i grundskolan åk 4–6` ≠ kursplanens namn `Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`); rad: - &lt;a class="no-graph" href="GPG2LZ"&gt;Sociala relationer, konflikter och makt i grundskolan åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp); rad: - Engelska för grundlärare åk 4-6 1B, 15 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i grundskolan åk 4–6` ≠ kursplanens namn `Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`); rad: - &lt;a class="no-graph" href="GPG2LZ"&gt;Sociala relationer, konflikter och makt i grundskolan åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1356,14 +1356,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - [[GSV2ZV|Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
+          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - [[GSV2ZW|Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning]], 15 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1653,14 +1653,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1707,14 +1707,14 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1761,14 +1761,14 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1788,14 +1788,14 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1815,14 +1815,14 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
+          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1940,24 +1940,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1967,24 +1967,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,24 +2021,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
+          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,373 +2129,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare 4-6` (kurskod `GSV2ZU`); rad: - [[GSV2ZU|Svenska 1 för grundlärare 4–6: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur]], 15 hp</t>
+          <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Programtext `Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare 4-6` (kurskod `GSV2ZX`); rad: - [[GSV2ZX|Svenska 2 för grundlärare 4–6: Läs- och skrivutveckling och läs och skrivundervisning]], 15 hp</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E76"/>
+  <autoFilter ref="A1:E63"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2621,32 +2270,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -973,7 +973,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i grundskolan åk 4–6` ≠ kursplanens namn `Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`); rad: - &lt;a class="no-graph" href="GPG2LZ"&gt;Sociala relationer, konflikter och makt i grundskolan åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LL46A</t>
+          <t>LLF3A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LLF3A</t>
+          <t>LLL3A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - &lt;a class="no-graph" href="GPG3CF"&gt;Utveckling och lärande i förskoleklass och grundskolans åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - &lt;a class="no-graph" href="GPG2M9"&gt;Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3&lt;/a&gt;, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LLL3A</t>
+          <t>LLL6A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LLL6A</t>
+          <t>LLP6A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,17 +1589,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LU79A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LUGYA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LLP6A</t>
+          <t>LYSLA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,395 +1756,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+          <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Programtext `Utveckling och lärande i grundskolans åk 4–6` ≠ kursplanens namn `Utveckling och lärande i grundskolans åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG3CG`); rad: - &lt;a class="no-graph" href="GPG3CG"&gt;Utveckling och lärande i grundskolans åk 4–6&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>LLP6A</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>LU79A</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Programtext `Undervisning och ledarskap – KPU` ≠ kursplanens namn `Undervisning och ledarskap - KPU (varav 10 hp VFU)` (kurskod `GPG2RH`); rad: - &lt;a class="no-graph" href="GPG2RH"&gt;Undervisning och ledarskap – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Programtext `Ämnesdidaktik och specialpedagogik – KPU` ≠ kursplanens namn `Ämnesdidaktik och specialpedagogik - KPU (varav 10 hp VFU)` (kurskod `GPG2S8`); rad: - &lt;a class="no-graph" href="GPG2S8"&gt;Ämnesdidaktik och specialpedagogik – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>LUGYA</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Programtext `Professionellt lärarskap och skolutveckling – KPU` ≠ kursplanens namn `Professionellt lärarskap och skolutveckling - KPU (varav 10 hp VFU)` (kurskod `APG27Z`); rad: - &lt;a class="no-graph" href="APG27Z"&gt;Professionellt lärarskap och skolutveckling – KPU&lt;/a&gt;, 15 hp</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>LYSLA</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E63"/>
+  <autoFilter ref="A1:E49"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2242,34 +1864,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp); rad: - Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv, 7,5 hp</t>
+          <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp); rad: - Kärnområden i tillämpad engelsk lingvistik, 7,5 hp</t>
+          <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp); rad: - Engelska för grundlärare åk 4-6 1A, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1A` (15 hp)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp); rad: - Engelska för grundlärare åk 4-6 1B, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1B` (15 hp)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - &lt;a class="no-graph" href="APG244"&gt;Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - [[GEN2BJ|Engelska för grundlärare åk F-3]], 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp); rad: - Didaktik och ledarskap i grundskolans åk 4–6, 15 hp</t>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 1, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp); rad: - Examensarbete för grundlärarexamen inriktning 4–6 – del 2, 15 hp</t>
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp); rad: - Utvärdering och utvecklingsarbete i grundskolans åk 4–6, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp); rad: - Engelska för grundlärare åk 4-6 1a, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp); rad: - Engelska för grundlärare åk 4-6 1b, 15 hp</t>
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp); rad: - Sociala relationer, konflikter och makt i grundskolan åk 4–6,, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`); rad: - &lt;a class="no-graph" href="GPG2SC"&gt;Samhällsorienterande ämnen, åk 4–6&lt;/a&gt;, 30 hp</t>
+          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`); rad: - &lt;a class="no-graph" href="APG282"&gt;Examensarbete för ämneslärare&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`Undervisning och ledarskap` (15 hp); rad: - Undervisning och ledarskap, 15 hp</t>
+          <t>`Undervisning och ledarskap` (15 hp)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`Ämnesdidaktik och specialpedagogik` (15 hp); rad: - Ämnesdidaktik och specialpedagogik, 15 hp</t>
+          <t>`Ämnesdidaktik och specialpedagogik` (15 hp)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Professionellt lärarskap och skolutveckling` (15 hp); rad: - Professionellt lärarskap och skolutveckling, 15 hp</t>
+          <t>`Professionellt lärarskap och skolutveckling` (15 hp)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">

--- a/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$G$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2020-04-17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HSVAA</t>
         </is>
@@ -509,15 +531,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
         </is>
@@ -536,15 +564,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -563,15 +601,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -590,15 +638,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -617,15 +675,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -644,15 +712,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -671,15 +749,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -698,15 +786,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -725,15 +823,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -752,15 +860,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -779,15 +897,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -806,15 +934,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -833,15 +967,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -860,15 +1000,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -887,15 +1033,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -914,15 +1066,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>`Engelska för grundlärare åk 4-6 1A` (15 hp)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -941,15 +1099,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>`Engelska för grundlärare åk 4-6 1B` (15 hp)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -968,15 +1132,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -995,15 +1165,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
@@ -1022,15 +1198,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
@@ -1049,15 +1231,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
@@ -1076,15 +1264,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
@@ -1103,15 +1297,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
@@ -1130,15 +1330,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
@@ -1157,15 +1363,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
@@ -1184,15 +1396,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
@@ -1211,15 +1429,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1238,15 +1462,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1265,15 +1495,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1292,15 +1528,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1319,15 +1561,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>`Engelska för grundlärare åk 4-6 1a` (15 hp)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1346,15 +1594,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>`Engelska för grundlärare åk 4-6 1b` (15 hp)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1373,15 +1627,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1400,15 +1660,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1427,15 +1693,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1454,15 +1726,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1481,15 +1759,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1508,15 +1792,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1535,15 +1825,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>`Engelska för grundlärare åk 4-6 1a` (15 hp)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1562,15 +1858,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>`Engelska för grundlärare åk 4-6 1b` (15 hp)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1589,15 +1891,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1616,15 +1924,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1643,15 +1957,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
@@ -1670,15 +1994,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
@@ -1697,15 +2031,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>`Undervisning och ledarskap` (15 hp)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
@@ -1724,15 +2064,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>`Ämnesdidaktik och specialpedagogik` (15 hp)</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
@@ -1751,119 +2097,125 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>`Professionellt lärarskap och skolutveckling` (15 hp)</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E49"/>
+  <autoFilter ref="A1:G49"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$G$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$H$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -504,7 +510,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -512,7 +518,12 @@
           <t>`Svenska som andraspråk i ett utvecklingsperspektiv - vetenskapsteoretiska förklaringsmodeller och metodologiska perspektiv` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>`Svenska som andraspråk i ett utvecklingsperspektiv - förklaringsmodeller och metodologiska perspektiv` (kurskod `SS3003`)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HSVAA</t>
         </is>
@@ -537,7 +548,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -545,7 +556,12 @@
           <t>`Kärnområden i tillämpad engelsk lingvistik` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>`Kärnområden inom tillämpad engelsk lingvistik` (kurskod `EN3076`)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HTESA</t>
         </is>
@@ -582,7 +598,8 @@
           <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -616,10 +633,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -648,15 +666,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9 (varav 7,5 hp VFU)` (kurskod `GPG328`)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -685,15 +708,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -722,15 +750,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -764,10 +797,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -801,10 +835,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -833,15 +868,20 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan (inkl 7,5 hp VFU)` (kurskod `GPG3KB`)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -870,15 +910,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -907,15 +952,20 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -940,7 +990,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -948,7 +998,12 @@
           <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i grundskolans årskurs 4-6 (inkl 7,5 hp VFU)` (kurskod `GPG3CJ`)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -973,7 +1028,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -981,7 +1036,12 @@
           <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>`Examensarbete för grundlärarexamen inriktning 4-6 del 1` (kurskod `GPG2E7`)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -1006,7 +1066,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1014,7 +1074,12 @@
           <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>`Examensarbete för grundlärarexamen inriktning 4-6 del 2` (kurskod `APG247`)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -1039,7 +1104,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1047,7 +1112,12 @@
           <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4-6, (varav 7,5 hp VFU)` (kurskod `APG276`)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -1072,7 +1142,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1080,7 +1150,12 @@
           <t>`Engelska för grundlärare åk 4-6 1A` (15 hp)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare åk 4-6, 1A` (kurskod `GEN2BK`)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -1105,7 +1180,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1113,7 +1188,12 @@
           <t>`Engelska för grundlärare åk 4-6 1B` (15 hp)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare åk 4-6, 1B` (kurskod `GEN2LD`)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -1143,10 +1223,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+          <t>`Samhällsorienterande ämnen, åk 4–6`</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>`Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LL46A</t>
         </is>
@@ -1171,7 +1256,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1179,7 +1264,12 @@
           <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans årskurs 1-3 (inkl 7,5 hp VFU)` (kurskod `GPG3CH`)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
@@ -1204,7 +1294,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1212,7 +1302,12 @@
           <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `APG275`)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
@@ -1242,10 +1337,15 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3`</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
@@ -1275,10 +1375,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+          <t>`Engelska för grundlärare åk F-3`</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
@@ -1303,7 +1408,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1311,7 +1416,12 @@
           <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans årskurs 1-3 (inkl 7,5 hp VFU)` (kurskod `GPG3CH`)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
@@ -1336,7 +1446,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1344,7 +1454,12 @@
           <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `APG275`)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
@@ -1374,10 +1489,15 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3`</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
@@ -1407,10 +1527,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+          <t>`Engelska för grundlärare åk F-3`</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
@@ -1435,15 +1560,16 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1468,15 +1594,20 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i grundskolans årskurs 4-6 (inkl 7,5 hp VFU)` (kurskod `GPG3CJ`)</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1501,15 +1632,20 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>`Examensarbete för grundlärarexamen inriktning 4-6 del 1` (kurskod `GPG2E7`)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1534,15 +1670,20 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>`Examensarbete för grundlärarexamen inriktning 4-6 del 2` (kurskod `APG247`)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1567,15 +1708,20 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4-6, (varav 7,5 hp VFU)` (kurskod `APG276`)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1600,15 +1746,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare åk 4-6, 1A` (kurskod `GEN2BK`)</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1633,15 +1784,20 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare åk 4-6, 1B` (kurskod `GEN2LD`)</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1671,10 +1827,15 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+          <t>`Samhällsorienterande ämnen, åk 4–6`</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>`Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
         </is>
@@ -1699,15 +1860,16 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1732,15 +1894,20 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i grundskolans årskurs 4-6 (inkl 7,5 hp VFU)` (kurskod `GPG3CJ`)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1765,15 +1932,20 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 1` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>`Examensarbete för grundlärarexamen inriktning 4-6 del 1` (kurskod `GPG2E7`)</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1798,15 +1970,20 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+          <t>`Examensarbete för grundlärarexamen inriktning 4–6 – del 2` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>`Examensarbete för grundlärarexamen inriktning 4-6 del 2` (kurskod `APG247`)</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1831,15 +2008,20 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4–6` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 4-6, (varav 7,5 hp VFU)` (kurskod `APG276`)</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1864,15 +2046,20 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+          <t>`Engelska för grundlärare åk 4-6 1a` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare åk 4-6, 1A` (kurskod `GEN2BK`)</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1897,15 +2084,20 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+          <t>`Engelska för grundlärare åk 4-6 1b` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare åk 4-6, 1B` (kurskod `GEN2LD`)</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1935,10 +2127,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsorienterande ämnen, åk 4–6` ≠ kursplanens namn `Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+          <t>`Samhällsorienterande ämnen, åk 4–6`</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>`Samhällsorienterande ämnen, årskurs 4-6` (kurskod `GPG2SC`)</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
         </is>
@@ -1972,10 +2169,15 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`)</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+          <t>`Examensarbete för ämneslärare`</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>`Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`)</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LU79A</t>
         </is>
@@ -2009,10 +2211,15 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete för ämneslärare` ≠ kursplanens namn `Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`)</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+          <t>`Examensarbete för ämneslärare`</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>`Examensarbete för ämneslärare (avancerad nivå)` (kurskod `APG282`)</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LUGYA</t>
         </is>
@@ -2037,7 +2244,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2045,7 +2252,12 @@
           <t>`Undervisning och ledarskap` (15 hp)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>`Undervisning och ledarskap (varav 10 hp VFU)` (kurskod `GPG2QP`)</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
@@ -2070,7 +2282,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2078,7 +2290,12 @@
           <t>`Ämnesdidaktik och specialpedagogik` (15 hp)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>`Ämnesdidaktik och specialpedagogik (varav 10 hp VFU)` (kurskod `GPG2RS`)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
@@ -2103,7 +2320,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2111,111 +2328,116 @@
           <t>`Professionellt lärarskap och skolutveckling` (15 hp)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>`Professionellt lärarskap och skolutveckling (varav 10 hp VFU)` (kurskod `GPG3EV`)</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LYSLA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G49"/>
+  <autoFilter ref="A1:H49"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Programkurser olänkade.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -598,7 +598,11 @@
           <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9 (varav 7,5 hp VFU)` (kurskod `GPG328`)</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
@@ -628,15 +632,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9 (varav 7,5 hp VFU)` (kurskod `GPG328`)</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
@@ -671,12 +679,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9 (varav 7,5 hp VFU)` (kurskod `GPG328`)</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -713,12 +721,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -755,12 +763,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
+          <t>`Verksamhetsförlagd utbildning i grundskolan årskurs 7-9` (kurskod `APG28S`)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -792,15 +800,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan (inkl 7,5 hp VFU)` (kurskod `GPG3KB`)</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
@@ -830,15 +842,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>`Utveckling och lärande för ämneslärare inriktning gymnasieskolan (varav 7,5 hp VFU)` (kurskod `GPG329`)</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
@@ -873,12 +889,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan (inkl 7,5 hp VFU)` (kurskod `GPG3KB`)</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -915,12 +931,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -957,12 +973,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
+          <t>`Verksamhetsförlagd utbildning i gymnasieskolan` (kurskod `APG28R`)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1560,15 +1576,19 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i grundskolans årskurs 4-6 (inkl 7,5 hp VFU)` (kurskod `GPG3CJ`)</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL6A</t>
@@ -1599,12 +1619,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans årskurs 4-6 (inkl 7,5 hp VFU)` (kurskod `GPG3CJ`)</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1860,15 +1880,19 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i grundskolans årskurs 4-6 (inkl 7,5 hp VFU)` (kurskod `GPG3CJ`)</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLP6A</t>
@@ -1899,12 +1923,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans åk 4–6` (15 hp)</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4–6,` (15 hp)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i grundskolans årskurs 4-6 (inkl 7,5 hp VFU)` (kurskod `GPG3CJ`)</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 4-6 (varav 7,5 hp VFU)` (kurskod `GPG2LZ`)</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
